--- a/data/xingguang/2025_11/xingguang.xlsx
+++ b/data/xingguang/2025_11/xingguang.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sales-dashboard\modelscope-full\data\xingguang\2025_11\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9324"/>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58330,7 +58335,7 @@
         <v>0</v>
       </c>
       <c r="AC673" s="4">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="674" spans="1:29">
@@ -58472,7 +58477,7 @@
         <v>0</v>
       </c>
       <c r="AC675" s="4">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="676" spans="1:29">
@@ -58614,7 +58619,7 @@
         <v>0</v>
       </c>
       <c r="AC677" s="4">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="678" spans="1:29">
@@ -58685,7 +58690,7 @@
         <v>0</v>
       </c>
       <c r="AC678" s="4">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="679" spans="1:29">
@@ -59038,7 +59043,7 @@
         <v>0</v>
       </c>
       <c r="AC683" s="4">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="684" spans="1:29">
@@ -59176,7 +59181,7 @@
         <v>0</v>
       </c>
       <c r="AC685" s="4">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="686" spans="1:29">
@@ -59382,8 +59387,11 @@
       <c r="AB688" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="689" spans="1:28">
+      <c r="AC688" s="4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="689" spans="1:29">
       <c r="A689" s="7">
         <v>45979</v>
       </c>
@@ -59448,8 +59456,11 @@
       <c r="AB689" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="690" spans="1:28">
+      <c r="AC689" s="4">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="690" spans="1:29">
       <c r="A690" s="7">
         <v>45980</v>
       </c>
@@ -59514,8 +59525,11 @@
       <c r="AB690" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="691" spans="1:28">
+      <c r="AC690" s="4">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="691" spans="1:29">
       <c r="A691" s="7">
         <v>45981</v>
       </c>
@@ -59580,8 +59594,11 @@
       <c r="AB691" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="692" spans="1:28">
+      <c r="AC691" s="4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="692" spans="1:29">
       <c r="A692" s="7">
         <v>45982</v>
       </c>
@@ -59646,8 +59663,11 @@
       <c r="AB692" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="693" spans="1:28">
+      <c r="AC692" s="4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="693" spans="1:29">
       <c r="A693" s="7">
         <v>45983</v>
       </c>
@@ -59712,8 +59732,11 @@
       <c r="AB693" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="694" spans="1:28">
+      <c r="AC693" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="694" spans="1:29">
       <c r="A694" s="7">
         <v>45984</v>
       </c>
@@ -59778,8 +59801,11 @@
       <c r="AB694" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="695" spans="1:28">
+      <c r="AC694" s="4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="695" spans="1:29">
       <c r="A695" s="7">
         <v>45985</v>
       </c>
@@ -59844,8 +59870,11 @@
       <c r="AB695" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="696" spans="1:28">
+      <c r="AC695" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="696" spans="1:29">
       <c r="A696" s="7">
         <v>45986</v>
       </c>
@@ -59910,8 +59939,11 @@
       <c r="AB696" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="697" spans="1:28">
+      <c r="AC696" s="4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="697" spans="1:29">
       <c r="A697" s="7">
         <v>45987</v>
       </c>
@@ -59976,8 +60008,11 @@
       <c r="AB697" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="698" spans="1:28">
+      <c r="AC697" s="4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="698" spans="1:29">
       <c r="A698" s="7">
         <v>45988</v>
       </c>
@@ -60042,8 +60077,11 @@
       <c r="AB698" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="699" spans="1:28">
+      <c r="AC698" s="4">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="699" spans="1:29">
       <c r="A699" s="7">
         <v>45989</v>
       </c>
@@ -60108,8 +60146,11 @@
       <c r="AB699" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="700" spans="1:28">
+      <c r="AC699" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="700" spans="1:29">
       <c r="A700" s="7">
         <v>45990</v>
       </c>
@@ -60174,8 +60215,11 @@
       <c r="AB700" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="701" spans="1:28">
+      <c r="AC700" s="4">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="701" spans="1:29">
       <c r="A701" s="7">
         <v>45991</v>
       </c>
@@ -60240,8 +60284,11 @@
       <c r="AB701" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="702" spans="1:28">
+      <c r="AC701" s="4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="702" spans="1:29">
       <c r="A702" s="7">
         <v>45992</v>
       </c>
@@ -60300,12 +60347,11 @@
       <c r="Z702" s="4">
         <v>20</v>
       </c>
-      <c r="AA702" s="3"/>
       <c r="AB702" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:28">
+    <row r="703" spans="1:29">
       <c r="A703" s="7">
         <v>45993</v>
       </c>
@@ -60364,12 +60410,11 @@
       <c r="Z703" s="4">
         <v>20</v>
       </c>
-      <c r="AA703" s="3"/>
       <c r="AB703" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:28">
+    <row r="704" spans="1:29">
       <c r="A704" s="7">
         <v>45994</v>
       </c>
@@ -60428,7 +60473,6 @@
       <c r="Z704" s="4">
         <v>20</v>
       </c>
-      <c r="AA704" s="3"/>
       <c r="AB704" s="3">
         <v>0</v>
       </c>
@@ -60492,7 +60536,6 @@
       <c r="Z705" s="4">
         <v>20</v>
       </c>
-      <c r="AA705" s="3"/>
       <c r="AB705" s="3">
         <v>0</v>
       </c>
@@ -60556,7 +60599,6 @@
       <c r="Z706" s="4">
         <v>20</v>
       </c>
-      <c r="AA706" s="3"/>
       <c r="AB706" s="3">
         <v>0</v>
       </c>
@@ -60620,7 +60662,6 @@
       <c r="Z707" s="4">
         <v>20</v>
       </c>
-      <c r="AA707" s="3"/>
       <c r="AB707" s="3">
         <v>0</v>
       </c>
@@ -60684,7 +60725,6 @@
       <c r="Z708" s="4">
         <v>21</v>
       </c>
-      <c r="AA708" s="3"/>
       <c r="AB708" s="3">
         <v>0</v>
       </c>
@@ -60748,7 +60788,6 @@
       <c r="Z709" s="4">
         <v>21</v>
       </c>
-      <c r="AA709" s="3"/>
       <c r="AB709" s="3">
         <v>0</v>
       </c>
@@ -60812,7 +60851,6 @@
       <c r="Z710" s="4">
         <v>21</v>
       </c>
-      <c r="AA710" s="3"/>
       <c r="AB710" s="3">
         <v>0</v>
       </c>
@@ -60876,7 +60914,6 @@
       <c r="Z711" s="4">
         <v>21</v>
       </c>
-      <c r="AA711" s="3"/>
       <c r="AB711" s="3">
         <v>0</v>
       </c>
@@ -60940,7 +60977,6 @@
       <c r="Z712" s="4">
         <v>21</v>
       </c>
-      <c r="AA712" s="3"/>
       <c r="AB712" s="3">
         <v>0</v>
       </c>
@@ -61004,7 +61040,6 @@
       <c r="Z713" s="4">
         <v>21</v>
       </c>
-      <c r="AA713" s="3"/>
       <c r="AB713" s="3">
         <v>0</v>
       </c>
@@ -61068,7 +61103,6 @@
       <c r="Z714" s="4">
         <v>21</v>
       </c>
-      <c r="AA714" s="3"/>
       <c r="AB714" s="3">
         <v>0</v>
       </c>
@@ -61132,7 +61166,6 @@
       <c r="Z715" s="4">
         <v>21</v>
       </c>
-      <c r="AA715" s="3"/>
       <c r="AB715" s="3">
         <v>0</v>
       </c>
@@ -61196,7 +61229,6 @@
       <c r="Z716" s="4">
         <v>21</v>
       </c>
-      <c r="AA716" s="3"/>
       <c r="AB716" s="3">
         <v>0</v>
       </c>
@@ -61260,7 +61292,6 @@
       <c r="Z717" s="4">
         <v>21</v>
       </c>
-      <c r="AA717" s="3"/>
       <c r="AB717" s="3">
         <v>0</v>
       </c>
@@ -61324,7 +61355,6 @@
       <c r="Z718" s="4">
         <v>21</v>
       </c>
-      <c r="AA718" s="3"/>
       <c r="AB718" s="3">
         <v>0</v>
       </c>
@@ -61388,7 +61418,6 @@
       <c r="Z719" s="4">
         <v>21</v>
       </c>
-      <c r="AA719" s="3"/>
       <c r="AB719" s="3">
         <v>0</v>
       </c>
@@ -61452,7 +61481,6 @@
       <c r="Z720" s="4">
         <v>21</v>
       </c>
-      <c r="AA720" s="3"/>
       <c r="AB720" s="3">
         <v>0</v>
       </c>
@@ -61512,7 +61540,6 @@
       <c r="Z721" s="4">
         <v>21</v>
       </c>
-      <c r="AA721" s="3"/>
       <c r="AB721" s="3">
         <v>0</v>
       </c>
@@ -61572,7 +61599,6 @@
       <c r="Z722" s="4">
         <v>22</v>
       </c>
-      <c r="AA722" s="3"/>
       <c r="AB722" s="3">
         <v>0</v>
       </c>
@@ -61632,7 +61658,6 @@
       <c r="Z723" s="4">
         <v>22</v>
       </c>
-      <c r="AA723" s="3"/>
       <c r="AB723" s="3">
         <v>0</v>
       </c>
@@ -61692,7 +61717,6 @@
       <c r="Z724" s="4">
         <v>22</v>
       </c>
-      <c r="AA724" s="3"/>
       <c r="AB724" s="3">
         <v>0</v>
       </c>
@@ -61752,7 +61776,6 @@
       <c r="Z725" s="4">
         <v>22</v>
       </c>
-      <c r="AA725" s="3"/>
       <c r="AB725" s="3">
         <v>0</v>
       </c>
@@ -61812,7 +61835,6 @@
       <c r="Z726" s="4">
         <v>22</v>
       </c>
-      <c r="AA726" s="3"/>
       <c r="AB726" s="3">
         <v>0</v>
       </c>
@@ -61872,7 +61894,6 @@
       <c r="Z727" s="4">
         <v>22</v>
       </c>
-      <c r="AA727" s="3"/>
       <c r="AB727" s="3">
         <v>0</v>
       </c>
@@ -61932,7 +61953,6 @@
       <c r="Z728" s="4">
         <v>22</v>
       </c>
-      <c r="AA728" s="3"/>
       <c r="AB728" s="3">
         <v>0</v>
       </c>
@@ -61992,7 +62012,6 @@
       <c r="Z729" s="4">
         <v>22</v>
       </c>
-      <c r="AA729" s="3"/>
       <c r="AB729" s="3">
         <v>0</v>
       </c>
@@ -62052,7 +62071,6 @@
       <c r="Z730" s="4">
         <v>22</v>
       </c>
-      <c r="AA730" s="3"/>
       <c r="AB730" s="3">
         <v>0</v>
       </c>
@@ -62112,7 +62130,6 @@
       <c r="Z731" s="4">
         <v>22</v>
       </c>
-      <c r="AA731" s="3"/>
       <c r="AB731" s="3">
         <v>0</v>
       </c>
@@ -62172,7 +62189,6 @@
       <c r="Z732" s="4">
         <v>22</v>
       </c>
-      <c r="AA732" s="3"/>
       <c r="AB732" s="3">
         <v>1</v>
       </c>
